--- a/docs/from_CH/Exp1 Errors_Corrections_Template.xlsx
+++ b/docs/from_CH/Exp1 Errors_Corrections_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="280">
   <si>
     <t xml:space="preserve">Ignore all CBF1 files- data will not be analysed</t>
   </si>
@@ -626,10 +626,25 @@
     <t xml:space="preserve">Touch</t>
   </si>
   <si>
-    <t xml:space="preserve">Time(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GO/NOGO</t>
+    <t xml:space="preserve">ExperimentDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrialNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrialType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResponseTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResponseType</t>
   </si>
   <si>
     <t xml:space="preserve">Comment_Time</t>
@@ -659,9 +674,6 @@
     <t xml:space="preserve">ResponseCBs</t>
   </si>
   <si>
-    <t xml:space="preserve">ResponseTime</t>
-  </si>
-  <si>
     <t xml:space="preserve">CH</t>
   </si>
   <si>
@@ -704,7 +716,7 @@
     <t xml:space="preserve">Experiment_2023-10-08T11:03:05.275380_ash_4_Training - fixed.log</t>
   </si>
   <si>
-    <t xml:space="preserve">Change to NOGO</t>
+    <t xml:space="preserve">Horse released late – Change to NOGO</t>
   </si>
   <si>
     <t xml:space="preserve">NOGO, 30.0</t>
@@ -731,6 +743,9 @@
     <t xml:space="preserve">Experiment_2023-10-09T11:42:20.024754_ash_5_Training randomised Type 1.log</t>
   </si>
   <si>
+    <t xml:space="preserve">NoGo response when should be Go response - Change to NOGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Experiment_2023-10-09T15:25:36.471599_dougie_7_Training randomised Type 2.log</t>
   </si>
   <si>
@@ -785,9 +800,6 @@
     <t xml:space="preserve">Experiment_2023-10-22T11:36:41.453331_bonnie_79_Test Type 1.log</t>
   </si>
   <si>
-    <t xml:space="preserve">Trial time</t>
-  </si>
-  <si>
     <t xml:space="preserve">Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
   </si>
   <si>
@@ -804,6 +816,9 @@
   </si>
   <si>
     <t xml:space="preserve">Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wgsdewewf</t>
   </si>
   <si>
     <t xml:space="preserve">N </t>
@@ -1038,168 +1053,164 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5153,12 +5164,12 @@
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="19.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="8.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="11.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="6.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="11.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="22" width="11.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="23" width="8.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="24" width="10.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="23" width="12.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="24" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="23" width="15.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="22" width="72.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="22" width="80.99"/>
@@ -5171,46 +5182,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>6</v>
+        <v>199</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I1" s="25" t="s">
         <v>11</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5233,30 +5244,30 @@
         <v>10.6</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H2" s="31"/>
       <c r="I2" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L2" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M2" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N2" s="31" t="n">
         <f aca="false">F2</f>
         <v>10.6</v>
       </c>
       <c r="P2" s="33" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5279,23 +5290,23 @@
         <v>8.21</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H3" s="31"/>
       <c r="I3" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M3" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N3" s="31" t="n">
         <f aca="false">F3</f>
@@ -5322,26 +5333,26 @@
         <v>30</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H4" s="31"/>
       <c r="I4" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="M4" s="30" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N4" s="30" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5364,20 +5375,20 @@
         <v>30</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H5" s="31"/>
       <c r="I5" s="30" t="s">
         <v>39</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M5" s="30"/>
       <c r="N5" s="31" t="n">
@@ -5405,20 +5416,20 @@
         <v>8.95</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H6" s="31"/>
       <c r="I6" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L6" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M6" s="30" t="n">
         <v>12.3</v>
@@ -5448,23 +5459,23 @@
         <v>7.62</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H7" s="31"/>
       <c r="I7" s="30" t="s">
         <v>40</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L7" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M7" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N7" s="31" t="n">
         <f aca="false">F7</f>
@@ -5491,23 +5502,23 @@
         <v>9.21</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H8" s="31"/>
       <c r="I8" s="30" t="s">
         <v>41</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N8" s="31" t="n">
         <f aca="false">F8</f>
@@ -5534,23 +5545,23 @@
         <v>10.09</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="30" t="s">
         <v>44</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N9" s="31" t="n">
         <f aca="false">F9</f>
@@ -5577,23 +5588,23 @@
         <v>12.45</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H10" s="31"/>
       <c r="I10" s="30" t="s">
         <v>45</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L10" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M10" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N10" s="31" t="n">
         <f aca="false">F10</f>
@@ -5620,23 +5631,23 @@
         <v>9.29</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H11" s="31"/>
       <c r="I11" s="30" t="s">
         <v>46</v>
       </c>
       <c r="J11" s="30" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L11" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M11" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N11" s="31" t="n">
         <f aca="false">F11</f>
@@ -5663,23 +5674,23 @@
         <v>9.87</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K12" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L12" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M12" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N12" s="31" t="n">
         <f aca="false">F12</f>
@@ -5706,23 +5717,23 @@
         <v>8.22</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J13" s="30" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K13" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L13" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M13" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N13" s="31" t="n">
         <f aca="false">F13</f>
@@ -5749,23 +5760,23 @@
         <v>7.43</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="30" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L14" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M14" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N14" s="31" t="n">
         <f aca="false">F14</f>
@@ -5792,23 +5803,23 @@
         <v>6.56</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H15" s="31"/>
       <c r="I15" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J15" s="30" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K15" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L15" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M15" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N15" s="31" t="n">
         <f aca="false">F15</f>
@@ -5835,28 +5846,26 @@
         <v>48.49</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>224</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="H16" s="0"/>
       <c r="I16" s="30" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L16" s="30" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="M16" s="30" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N16" s="30" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5879,23 +5888,23 @@
         <v>9.43</v>
       </c>
       <c r="G17" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H17" s="31"/>
       <c r="I17" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L17" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M17" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N17" s="31" t="n">
         <f aca="false">F17</f>
@@ -5922,23 +5931,23 @@
         <v>9.08</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H18" s="31"/>
       <c r="I18" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L18" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M18" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N18" s="31" t="n">
         <f aca="false">F18</f>
@@ -5965,23 +5974,23 @@
         <v>7.95</v>
       </c>
       <c r="G19" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H19" s="31"/>
       <c r="I19" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L19" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M19" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N19" s="31" t="n">
         <f aca="false">F19</f>
@@ -6008,23 +6017,23 @@
         <v>6.45</v>
       </c>
       <c r="G20" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H20" s="31"/>
       <c r="I20" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L20" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M20" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N20" s="31" t="n">
         <f aca="false">F20</f>
@@ -6051,23 +6060,23 @@
         <v>7.11</v>
       </c>
       <c r="G21" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H21" s="31"/>
       <c r="I21" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K21" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L21" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M21" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N21" s="31" t="n">
         <f aca="false">F21</f>
@@ -6094,23 +6103,23 @@
         <v>6.24</v>
       </c>
       <c r="G22" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H22" s="31"/>
       <c r="I22" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K22" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L22" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M22" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N22" s="31" t="n">
         <f aca="false">F22</f>
@@ -6125,7 +6134,7 @@
         <v>48</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D23" s="30" t="n">
         <v>9</v>
@@ -6137,23 +6146,23 @@
         <v>8.55</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H23" s="31"/>
       <c r="I23" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J23" s="30" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K23" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L23" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M23" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N23" s="31" t="n">
         <f aca="false">F23</f>
@@ -6168,7 +6177,7 @@
         <v>48</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D24" s="30" t="n">
         <v>11</v>
@@ -6180,23 +6189,23 @@
         <v>7.95</v>
       </c>
       <c r="G24" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H24" s="31"/>
       <c r="I24" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J24" s="30" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L24" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M24" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N24" s="31" t="n">
         <f aca="false">F24</f>
@@ -6223,23 +6232,23 @@
         <v>8.09</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H25" s="31"/>
       <c r="I25" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J25" s="30" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L25" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M25" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N25" s="31" t="n">
         <f aca="false">F25</f>
@@ -6266,23 +6275,23 @@
         <v>8.69</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="30" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L26" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M26" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N26" s="31" t="n">
         <f aca="false">F26</f>
@@ -6309,23 +6318,23 @@
         <v>12.88</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H27" s="31"/>
       <c r="I27" s="30" t="s">
         <v>54</v>
       </c>
       <c r="J27" s="30" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K27" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L27" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M27" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N27" s="31" t="n">
         <f aca="false">F27</f>
@@ -6352,23 +6361,23 @@
         <v>30</v>
       </c>
       <c r="G28" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H28" s="31"/>
       <c r="I28" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J28" s="30" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K28" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L28" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M28" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N28" s="31" t="n">
         <f aca="false">F28</f>
@@ -6395,23 +6404,23 @@
         <v>21.29</v>
       </c>
       <c r="G29" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="30" t="s">
         <v>45</v>
       </c>
       <c r="J29" s="30" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L29" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M29" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N29" s="31" t="n">
         <f aca="false">F29</f>
@@ -6438,16 +6447,14 @@
         <v>43.14</v>
       </c>
       <c r="G30" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="H30" s="31" t="s">
-        <v>224</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="H30" s="31"/>
       <c r="I30" s="30" t="s">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c r="J30" s="30" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K30" s="30"/>
       <c r="L30" s="30"/>
@@ -6474,14 +6481,14 @@
         <v>10.68</v>
       </c>
       <c r="G31" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H31" s="31"/>
       <c r="I31" s="30" t="s">
         <v>55</v>
       </c>
       <c r="J31" s="30" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K31" s="30"/>
       <c r="L31" s="30"/>
@@ -6508,14 +6515,14 @@
         <v>9.26</v>
       </c>
       <c r="G32" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H32" s="31"/>
       <c r="I32" s="30" t="s">
         <v>55</v>
       </c>
       <c r="J32" s="30" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K32" s="30"/>
       <c r="L32" s="30"/>
@@ -6542,14 +6549,14 @@
         <v>30</v>
       </c>
       <c r="G33" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H33" s="31"/>
       <c r="I33" s="30" t="s">
         <v>55</v>
       </c>
       <c r="J33" s="30" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K33" s="30"/>
       <c r="L33" s="30"/>
@@ -6576,14 +6583,14 @@
         <v>10.62</v>
       </c>
       <c r="G34" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H34" s="31"/>
       <c r="I34" s="30" t="s">
         <v>55</v>
       </c>
       <c r="J34" s="30" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K34" s="30"/>
       <c r="L34" s="30"/>
@@ -6610,14 +6617,14 @@
         <v>12.54</v>
       </c>
       <c r="G35" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H35" s="31"/>
       <c r="I35" s="30" t="s">
         <v>62</v>
       </c>
       <c r="J35" s="30" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K35" s="30"/>
       <c r="L35" s="30"/>
@@ -6644,14 +6651,14 @@
         <v>10.23</v>
       </c>
       <c r="G36" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H36" s="31"/>
       <c r="I36" s="30" t="s">
         <v>54</v>
       </c>
       <c r="J36" s="30" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K36" s="30"/>
       <c r="L36" s="30"/>
@@ -6678,14 +6685,14 @@
         <v>30</v>
       </c>
       <c r="G37" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H37" s="31"/>
       <c r="I37" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K37" s="30"/>
       <c r="L37" s="30"/>
@@ -6710,14 +6717,14 @@
       </c>
       <c r="F38" s="31"/>
       <c r="G38" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H38" s="31"/>
       <c r="I38" s="30" t="s">
         <v>63</v>
       </c>
       <c r="J38" s="30" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K38" s="30"/>
       <c r="L38" s="30"/>
@@ -6744,14 +6751,14 @@
         <v>24.74</v>
       </c>
       <c r="G39" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H39" s="31"/>
       <c r="I39" s="30" t="s">
         <v>65</v>
       </c>
       <c r="J39" s="30" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K39" s="30"/>
       <c r="L39" s="30"/>
@@ -6776,14 +6783,14 @@
         <v>9.49</v>
       </c>
       <c r="G40" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H40" s="31"/>
       <c r="I40" s="30" t="s">
         <v>66</v>
       </c>
       <c r="J40" s="30" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K40" s="30"/>
       <c r="L40" s="30"/>
@@ -6808,14 +6815,14 @@
         <v>11.81</v>
       </c>
       <c r="G41" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="30" t="s">
         <v>69</v>
       </c>
       <c r="J41" s="30" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
@@ -6842,14 +6849,14 @@
         <v>30</v>
       </c>
       <c r="G42" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H42" s="31"/>
       <c r="I42" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J42" s="30" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K42" s="30"/>
       <c r="L42" s="30"/>
@@ -6876,14 +6883,14 @@
         <v>9.87</v>
       </c>
       <c r="G43" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H43" s="31"/>
       <c r="I43" s="30" t="s">
         <v>113</v>
       </c>
       <c r="J43" s="30" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K43" s="30"/>
       <c r="L43" s="30"/>
@@ -6910,12 +6917,12 @@
         <v>12.08</v>
       </c>
       <c r="G44" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H44" s="31"/>
       <c r="I44" s="30"/>
       <c r="J44" s="30" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K44" s="30"/>
       <c r="L44" s="30"/>
@@ -6942,14 +6949,14 @@
         <v>7.96</v>
       </c>
       <c r="G45" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H45" s="31"/>
       <c r="I45" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J45" s="30" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K45" s="30"/>
       <c r="L45" s="30"/>
@@ -6974,14 +6981,14 @@
         <v>11.08</v>
       </c>
       <c r="G46" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H46" s="31"/>
       <c r="I46" s="30" t="s">
         <v>54</v>
       </c>
       <c r="J46" s="30" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K46" s="30"/>
       <c r="L46" s="30"/>
@@ -7008,14 +7015,14 @@
         <v>8.76</v>
       </c>
       <c r="G47" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H47" s="31"/>
       <c r="I47" s="30" t="s">
         <v>66</v>
       </c>
       <c r="J47" s="30" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K47" s="30"/>
       <c r="L47" s="30"/>
@@ -7042,14 +7049,14 @@
         <v>10.48</v>
       </c>
       <c r="G48" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="30" t="s">
         <v>17</v>
       </c>
       <c r="J48" s="30" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K48" s="30"/>
       <c r="L48" s="30"/>
@@ -7076,14 +7083,14 @@
         <v>30</v>
       </c>
       <c r="G49" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H49" s="31"/>
       <c r="I49" s="30" t="s">
         <v>84</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K49" s="30"/>
       <c r="L49" s="30"/>
@@ -7110,14 +7117,14 @@
         <v>7.89</v>
       </c>
       <c r="G50" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H50" s="31"/>
       <c r="I50" s="30" t="s">
         <v>62</v>
       </c>
       <c r="J50" s="30" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K50" s="30"/>
       <c r="L50" s="30"/>
@@ -7144,14 +7151,14 @@
         <v>7.36</v>
       </c>
       <c r="G51" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H51" s="31"/>
       <c r="I51" s="30" t="s">
         <v>54</v>
       </c>
       <c r="J51" s="30" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K51" s="30"/>
       <c r="L51" s="30"/>
@@ -7178,14 +7185,14 @@
         <v>30</v>
       </c>
       <c r="G52" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H52" s="31"/>
       <c r="I52" s="30" t="s">
         <v>87</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K52" s="30"/>
       <c r="L52" s="30"/>
@@ -7212,14 +7219,14 @@
         <v>7.84</v>
       </c>
       <c r="G53" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H53" s="31"/>
       <c r="I53" s="30" t="s">
         <v>17</v>
       </c>
       <c r="J53" s="30" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K53" s="30"/>
       <c r="L53" s="30"/>
@@ -7246,14 +7253,14 @@
         <v>7.65</v>
       </c>
       <c r="G54" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H54" s="31"/>
       <c r="I54" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J54" s="30" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K54" s="30"/>
       <c r="L54" s="30"/>
@@ -7280,14 +7287,14 @@
         <v>30</v>
       </c>
       <c r="G55" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H55" s="31"/>
       <c r="I55" s="30" t="s">
         <v>101</v>
       </c>
       <c r="J55" s="30" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K55" s="30"/>
       <c r="L55" s="30"/>
@@ -7299,7 +7306,7 @@
         <v>45219</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C56" s="30" t="s">
         <v>29</v>
@@ -7314,14 +7321,14 @@
         <v>11.59</v>
       </c>
       <c r="G56" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H56" s="31"/>
       <c r="I56" s="30" t="s">
         <v>17</v>
       </c>
       <c r="J56" s="30" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K56" s="30"/>
       <c r="L56" s="30"/>
@@ -7348,7 +7355,7 @@
         <v>30</v>
       </c>
       <c r="G57" s="32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H57" s="31"/>
       <c r="I57" s="30" t="s">
@@ -7380,14 +7387,14 @@
         <v>7.24</v>
       </c>
       <c r="G58" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H58" s="31"/>
       <c r="I58" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K58" s="30"/>
       <c r="L58" s="30"/>
@@ -7414,14 +7421,14 @@
         <v>7.97</v>
       </c>
       <c r="G59" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H59" s="31"/>
       <c r="I59" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J59" s="30" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K59" s="30"/>
       <c r="L59" s="30"/>
@@ -7448,14 +7455,14 @@
         <v>8.48</v>
       </c>
       <c r="G60" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H60" s="31"/>
       <c r="I60" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J60" s="30" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K60" s="30"/>
       <c r="L60" s="30"/>
@@ -7482,14 +7489,14 @@
         <v>7.7</v>
       </c>
       <c r="G61" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H61" s="31"/>
       <c r="I61" s="30" t="s">
         <v>50</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K61" s="30"/>
       <c r="L61" s="30"/>
@@ -7516,14 +7523,14 @@
         <v>20.3</v>
       </c>
       <c r="G62" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H62" s="31"/>
       <c r="I62" s="30" t="s">
         <v>109</v>
       </c>
       <c r="J62" s="30" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K62" s="30"/>
       <c r="L62" s="30"/>
@@ -7550,14 +7557,14 @@
         <v>7.1</v>
       </c>
       <c r="G63" s="32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H63" s="31"/>
       <c r="I63" s="30" t="s">
         <v>109</v>
       </c>
       <c r="J63" s="30" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K63" s="30"/>
       <c r="L63" s="30"/>
@@ -7583,15 +7590,16 @@
   <dimension ref="A1:N253"/>
   <sheetFormatPr defaultColWidth="10.52734375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="8.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="6.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="22" width="11.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="35" width="10.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="22" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="22" width="66.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="22" width="67.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="14.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="11.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="7.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="11.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="22" width="9.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="12.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="35" width="14.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="22" width="12.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="22" width="59.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="22" width="67.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="22" width="22.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="22" width="27.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="22" width="13.68"/>
@@ -7600,46 +7608,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>6</v>
+        <v>199</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="G1" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>200</v>
+        <v>202</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="I1" s="25" t="s">
         <v>11</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7661,24 +7669,24 @@
       <c r="F2" s="30" t="n">
         <v>10.93</v>
       </c>
-      <c r="G2" s="37" t="s">
-        <v>206</v>
+      <c r="G2" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H2" s="30"/>
       <c r="I2" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L2" s="30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M2" s="30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N2" s="31" t="n">
         <f aca="false">F2</f>
@@ -7704,27 +7712,27 @@
       <c r="F3" s="30" t="n">
         <v>11.81</v>
       </c>
-      <c r="G3" s="37" t="s">
-        <v>206</v>
+      <c r="G3" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H3" s="30"/>
       <c r="I3" s="30" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="M3" s="30" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="N3" s="30" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7746,15 +7754,15 @@
       <c r="F4" s="30" t="n">
         <v>6.24</v>
       </c>
-      <c r="G4" s="37" t="s">
-        <v>206</v>
+      <c r="G4" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H4" s="30"/>
       <c r="I4" s="30" t="s">
         <v>123</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K4" s="30"/>
       <c r="L4" s="30"/>
@@ -7780,15 +7788,15 @@
       <c r="F5" s="30" t="n">
         <v>18.08</v>
       </c>
-      <c r="G5" s="37" t="s">
-        <v>206</v>
+      <c r="G5" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H5" s="30"/>
       <c r="I5" s="30" t="s">
         <v>54</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K5" s="30"/>
       <c r="L5" s="30"/>
@@ -7814,15 +7822,15 @@
       <c r="F6" s="30" t="n">
         <v>9.29</v>
       </c>
-      <c r="G6" s="37" t="s">
-        <v>206</v>
+      <c r="G6" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H6" s="30"/>
       <c r="I6" s="30" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K6" s="30"/>
       <c r="L6" s="30"/>
@@ -7848,8 +7856,8 @@
       <c r="F7" s="30" t="n">
         <v>12.82</v>
       </c>
-      <c r="G7" s="37" t="s">
-        <v>206</v>
+      <c r="G7" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H7" s="30"/>
       <c r="I7" s="30" t="s">
@@ -7880,16 +7888,27 @@
       <c r="F8" s="30" t="n">
         <v>12.45</v>
       </c>
-      <c r="G8" s="37" t="s">
-        <v>206</v>
+      <c r="G8" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
+      <c r="J8" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="L8" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="N8" s="30" t="n">
+        <f aca="false">F8</f>
+        <v>12.45</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="n">
@@ -7910,8 +7929,8 @@
       <c r="F9" s="30" t="n">
         <v>11.97</v>
       </c>
-      <c r="G9" s="37" t="s">
-        <v>206</v>
+      <c r="G9" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
@@ -7940,8 +7959,8 @@
       <c r="F10" s="30" t="n">
         <v>26.66</v>
       </c>
-      <c r="G10" s="37" t="s">
-        <v>206</v>
+      <c r="G10" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
@@ -7970,8 +7989,8 @@
       <c r="F11" s="30" t="n">
         <v>12.27</v>
       </c>
-      <c r="G11" s="37" t="s">
-        <v>206</v>
+      <c r="G11" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
@@ -8000,8 +8019,8 @@
       <c r="F12" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="37" t="s">
-        <v>212</v>
+      <c r="G12" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
@@ -8030,8 +8049,8 @@
       <c r="F13" s="30" t="n">
         <v>11.52</v>
       </c>
-      <c r="G13" s="37" t="s">
-        <v>206</v>
+      <c r="G13" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -8060,8 +8079,8 @@
       <c r="F14" s="30" t="n">
         <v>12.93</v>
       </c>
-      <c r="G14" s="37" t="s">
-        <v>206</v>
+      <c r="G14" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
@@ -8090,8 +8109,8 @@
       <c r="F15" s="30" t="n">
         <v>11.6</v>
       </c>
-      <c r="G15" s="37" t="s">
-        <v>206</v>
+      <c r="G15" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
@@ -8120,8 +8139,8 @@
       <c r="F16" s="30" t="n">
         <v>13.14</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>206</v>
+      <c r="G16" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H16" s="30"/>
       <c r="I16" s="30"/>
@@ -8145,13 +8164,13 @@
         <v>11</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F17" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G17" s="37" t="s">
-        <v>212</v>
+      <c r="G17" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H17" s="30"/>
       <c r="I17" s="30"/>
@@ -8175,13 +8194,13 @@
         <v>12</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F18" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G18" s="37" t="s">
-        <v>212</v>
+      <c r="G18" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
@@ -8205,13 +8224,13 @@
         <v>13</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F19" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G19" s="37" t="s">
-        <v>212</v>
+      <c r="G19" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H19" s="30"/>
       <c r="I19" s="30"/>
@@ -8235,13 +8254,13 @@
         <v>14</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F20" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G20" s="37" t="s">
-        <v>212</v>
+      <c r="G20" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H20" s="30"/>
       <c r="I20" s="30"/>
@@ -8265,13 +8284,13 @@
         <v>15</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F21" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="37" t="s">
-        <v>212</v>
+      <c r="G21" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H21" s="30"/>
       <c r="I21" s="30"/>
@@ -8295,13 +8314,13 @@
         <v>16</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F22" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G22" s="37" t="s">
-        <v>212</v>
+      <c r="G22" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H22" s="30"/>
       <c r="I22" s="30"/>
@@ -8325,13 +8344,13 @@
         <v>17</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F23" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G23" s="37" t="s">
-        <v>212</v>
+      <c r="G23" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H23" s="30"/>
       <c r="I23" s="30"/>
@@ -8355,13 +8374,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F24" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G24" s="37" t="s">
-        <v>212</v>
+      <c r="G24" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H24" s="30"/>
       <c r="I24" s="30"/>
@@ -8385,13 +8404,13 @@
         <v>19</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F25" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G25" s="37" t="s">
-        <v>212</v>
+      <c r="G25" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H25" s="30"/>
       <c r="I25" s="30"/>
@@ -8415,13 +8434,13 @@
         <v>20</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F26" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G26" s="37" t="s">
-        <v>212</v>
+      <c r="G26" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H26" s="30"/>
       <c r="I26" s="30"/>
@@ -8450,15 +8469,15 @@
       <c r="F27" s="30" t="n">
         <v>11.13</v>
       </c>
-      <c r="G27" s="37" t="s">
-        <v>206</v>
+      <c r="G27" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H27" s="30"/>
       <c r="I27" s="30" t="s">
         <v>129</v>
       </c>
       <c r="J27" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K27" s="30"/>
       <c r="L27" s="30"/>
@@ -8484,13 +8503,13 @@
       <c r="F28" s="30" t="n">
         <v>12.67</v>
       </c>
-      <c r="G28" s="37" t="s">
-        <v>206</v>
+      <c r="G28" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H28" s="30"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
@@ -8516,13 +8535,13 @@
       <c r="F29" s="30" t="n">
         <v>11.73</v>
       </c>
-      <c r="G29" s="37" t="s">
-        <v>206</v>
+      <c r="G29" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H29" s="30"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K29" s="30"/>
       <c r="L29" s="30"/>
@@ -8548,13 +8567,13 @@
       <c r="F30" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="G30" s="37" t="s">
-        <v>206</v>
+      <c r="G30" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H30" s="30"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K30" s="30"/>
       <c r="L30" s="30"/>
@@ -8580,13 +8599,13 @@
       <c r="F31" s="30" t="n">
         <v>12.4</v>
       </c>
-      <c r="G31" s="37" t="s">
-        <v>206</v>
+      <c r="G31" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K31" s="30"/>
       <c r="L31" s="30"/>
@@ -8612,13 +8631,13 @@
       <c r="F32" s="30" t="n">
         <v>12.94</v>
       </c>
-      <c r="G32" s="37" t="s">
-        <v>206</v>
+      <c r="G32" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H32" s="30"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K32" s="30"/>
       <c r="L32" s="30"/>
@@ -8644,13 +8663,13 @@
       <c r="F33" s="30" t="n">
         <v>12.37</v>
       </c>
-      <c r="G33" s="37" t="s">
-        <v>206</v>
+      <c r="G33" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
       <c r="J33" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K33" s="30"/>
       <c r="L33" s="30"/>
@@ -8676,13 +8695,13 @@
       <c r="F34" s="30" t="n">
         <v>26.7</v>
       </c>
-      <c r="G34" s="37" t="s">
-        <v>206</v>
+      <c r="G34" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H34" s="30"/>
       <c r="I34" s="30"/>
       <c r="J34" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K34" s="30"/>
       <c r="L34" s="30"/>
@@ -8708,13 +8727,13 @@
       <c r="F35" s="30" t="n">
         <v>16.89</v>
       </c>
-      <c r="G35" s="37" t="s">
-        <v>206</v>
+      <c r="G35" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H35" s="30"/>
       <c r="I35" s="30"/>
       <c r="J35" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K35" s="30"/>
       <c r="L35" s="30"/>
@@ -8740,13 +8759,13 @@
       <c r="F36" s="30" t="n">
         <v>11.99</v>
       </c>
-      <c r="G36" s="37" t="s">
-        <v>206</v>
+      <c r="G36" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H36" s="30"/>
       <c r="I36" s="30"/>
       <c r="J36" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K36" s="30"/>
       <c r="L36" s="30"/>
@@ -8767,18 +8786,18 @@
         <v>11</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F37" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G37" s="37" t="s">
-        <v>212</v>
+      <c r="G37" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H37" s="30"/>
       <c r="I37" s="30"/>
       <c r="J37" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K37" s="30"/>
       <c r="L37" s="30"/>
@@ -8799,18 +8818,18 @@
         <v>12</v>
       </c>
       <c r="E38" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F38" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G38" s="37" t="s">
-        <v>212</v>
+      <c r="G38" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H38" s="30"/>
       <c r="I38" s="30"/>
       <c r="J38" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K38" s="30"/>
       <c r="L38" s="30"/>
@@ -8831,18 +8850,18 @@
         <v>13</v>
       </c>
       <c r="E39" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F39" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G39" s="37" t="s">
-        <v>212</v>
+      <c r="G39" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H39" s="30"/>
       <c r="I39" s="30"/>
       <c r="J39" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K39" s="30"/>
       <c r="L39" s="30"/>
@@ -8863,18 +8882,18 @@
         <v>14</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F40" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G40" s="37" t="s">
-        <v>212</v>
+      <c r="G40" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H40" s="30"/>
       <c r="I40" s="30"/>
       <c r="J40" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K40" s="30"/>
       <c r="L40" s="30"/>
@@ -8895,18 +8914,18 @@
         <v>15</v>
       </c>
       <c r="E41" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F41" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G41" s="37" t="s">
-        <v>212</v>
+      <c r="G41" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H41" s="30"/>
       <c r="I41" s="30"/>
       <c r="J41" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
@@ -8927,18 +8946,18 @@
         <v>16</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F42" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G42" s="37" t="s">
-        <v>212</v>
+      <c r="G42" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H42" s="30"/>
       <c r="I42" s="30"/>
       <c r="J42" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K42" s="30"/>
       <c r="L42" s="30"/>
@@ -8959,18 +8978,18 @@
         <v>17</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F43" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G43" s="37" t="s">
-        <v>212</v>
+      <c r="G43" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H43" s="30"/>
       <c r="I43" s="30"/>
       <c r="J43" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K43" s="30"/>
       <c r="L43" s="30"/>
@@ -8991,18 +9010,18 @@
         <v>18</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F44" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G44" s="37" t="s">
-        <v>212</v>
+      <c r="G44" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H44" s="30"/>
       <c r="I44" s="30"/>
       <c r="J44" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K44" s="30"/>
       <c r="L44" s="30"/>
@@ -9023,18 +9042,18 @@
         <v>19</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F45" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G45" s="37" t="s">
-        <v>212</v>
+      <c r="G45" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H45" s="30"/>
       <c r="I45" s="30"/>
       <c r="J45" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K45" s="30"/>
       <c r="L45" s="30"/>
@@ -9055,18 +9074,18 @@
         <v>20</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F46" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G46" s="37" t="s">
-        <v>212</v>
+      <c r="G46" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H46" s="30"/>
       <c r="I46" s="30"/>
       <c r="J46" s="30" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K46" s="30"/>
       <c r="L46" s="30"/>
@@ -9092,12 +9111,12 @@
       <c r="F47" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G47" s="37" t="s">
-        <v>212</v>
+      <c r="G47" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H47" s="30"/>
       <c r="I47" s="30" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J47" s="30"/>
       <c r="K47" s="30"/>
@@ -9124,8 +9143,8 @@
       <c r="F48" s="30" t="n">
         <v>28.2</v>
       </c>
-      <c r="G48" s="37" t="s">
-        <v>206</v>
+      <c r="G48" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H48" s="30"/>
       <c r="I48" s="30" t="s">
@@ -9156,13 +9175,13 @@
       <c r="F49" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G49" s="37" t="s">
-        <v>212</v>
+      <c r="G49" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H49" s="30"/>
       <c r="I49" s="30"/>
       <c r="J49" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K49" s="30"/>
       <c r="L49" s="30"/>
@@ -9188,13 +9207,13 @@
       <c r="F50" s="30" t="n">
         <v>10.07</v>
       </c>
-      <c r="G50" s="37" t="s">
-        <v>206</v>
+      <c r="G50" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H50" s="30"/>
       <c r="I50" s="30"/>
       <c r="J50" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K50" s="30"/>
       <c r="L50" s="30"/>
@@ -9220,13 +9239,13 @@
       <c r="F51" s="30" t="n">
         <v>13.74</v>
       </c>
-      <c r="G51" s="37" t="s">
-        <v>206</v>
+      <c r="G51" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H51" s="30"/>
       <c r="I51" s="30"/>
       <c r="J51" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K51" s="30"/>
       <c r="L51" s="30"/>
@@ -9252,13 +9271,13 @@
       <c r="F52" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G52" s="37" t="s">
-        <v>212</v>
+      <c r="G52" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H52" s="30"/>
       <c r="I52" s="30"/>
       <c r="J52" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K52" s="30"/>
       <c r="L52" s="30"/>
@@ -9284,13 +9303,13 @@
       <c r="F53" s="30" t="n">
         <v>10.08</v>
       </c>
-      <c r="G53" s="37" t="s">
-        <v>206</v>
+      <c r="G53" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H53" s="30"/>
       <c r="I53" s="30"/>
       <c r="J53" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K53" s="30"/>
       <c r="L53" s="30"/>
@@ -9316,13 +9335,13 @@
       <c r="F54" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G54" s="37" t="s">
-        <v>212</v>
+      <c r="G54" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H54" s="30"/>
       <c r="I54" s="30"/>
       <c r="J54" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K54" s="30"/>
       <c r="L54" s="30"/>
@@ -9348,13 +9367,13 @@
       <c r="F55" s="30" t="n">
         <v>10.46</v>
       </c>
-      <c r="G55" s="37" t="s">
-        <v>206</v>
+      <c r="G55" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H55" s="30"/>
       <c r="I55" s="30"/>
       <c r="J55" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K55" s="30"/>
       <c r="L55" s="30"/>
@@ -9380,13 +9399,13 @@
       <c r="F56" s="30" t="n">
         <v>11.93</v>
       </c>
-      <c r="G56" s="37" t="s">
-        <v>206</v>
+      <c r="G56" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H56" s="30"/>
       <c r="I56" s="30"/>
       <c r="J56" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K56" s="30"/>
       <c r="L56" s="30"/>
@@ -9412,13 +9431,13 @@
       <c r="F57" s="30" t="n">
         <v>11.33</v>
       </c>
-      <c r="G57" s="37" t="s">
-        <v>206</v>
+      <c r="G57" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H57" s="30"/>
       <c r="I57" s="30"/>
       <c r="J57" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K57" s="30"/>
       <c r="L57" s="30"/>
@@ -9444,13 +9463,13 @@
       <c r="F58" s="30" t="n">
         <v>10.93</v>
       </c>
-      <c r="G58" s="37" t="s">
-        <v>206</v>
+      <c r="G58" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H58" s="30"/>
       <c r="I58" s="30"/>
       <c r="J58" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K58" s="30"/>
       <c r="L58" s="30"/>
@@ -9476,13 +9495,13 @@
       <c r="F59" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G59" s="37" t="s">
-        <v>212</v>
+      <c r="G59" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H59" s="30"/>
       <c r="I59" s="30"/>
       <c r="J59" s="30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K59" s="30"/>
       <c r="L59" s="30"/>
@@ -9508,13 +9527,13 @@
       <c r="F60" s="30" t="n">
         <v>12.4</v>
       </c>
-      <c r="G60" s="37" t="s">
-        <v>206</v>
+      <c r="G60" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H60" s="30"/>
       <c r="I60" s="30"/>
       <c r="J60" s="30" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K60" s="30"/>
       <c r="L60" s="30"/>
@@ -9540,13 +9559,13 @@
       <c r="F61" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G61" s="37" t="s">
-        <v>212</v>
+      <c r="G61" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H61" s="30"/>
       <c r="I61" s="30"/>
       <c r="J61" s="30" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K61" s="30"/>
       <c r="L61" s="30"/>
@@ -9572,15 +9591,15 @@
       <c r="F62" s="30" t="n">
         <v>11.6</v>
       </c>
-      <c r="G62" s="37" t="s">
-        <v>206</v>
+      <c r="G62" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H62" s="30"/>
       <c r="I62" s="30" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="J62" s="30" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K62" s="30"/>
       <c r="L62" s="30"/>
@@ -9606,7 +9625,7 @@
       <c r="F63" s="30" t="n">
         <v>9.35</v>
       </c>
-      <c r="G63" s="37"/>
+      <c r="G63" s="36"/>
       <c r="H63" s="30"/>
       <c r="I63" s="30" t="s">
         <v>136</v>
@@ -9636,7 +9655,7 @@
       <c r="F64" s="30" t="n">
         <v>9.15</v>
       </c>
-      <c r="G64" s="37"/>
+      <c r="G64" s="36"/>
       <c r="H64" s="30"/>
       <c r="I64" s="30"/>
       <c r="J64" s="30"/>
@@ -9664,7 +9683,7 @@
       <c r="F65" s="30" t="n">
         <v>9.01</v>
       </c>
-      <c r="G65" s="37"/>
+      <c r="G65" s="36"/>
       <c r="H65" s="30"/>
       <c r="I65" s="30"/>
       <c r="J65" s="30"/>
@@ -9692,7 +9711,7 @@
       <c r="F66" s="30" t="n">
         <v>8.95</v>
       </c>
-      <c r="G66" s="37"/>
+      <c r="G66" s="36"/>
       <c r="H66" s="30"/>
       <c r="I66" s="30"/>
       <c r="J66" s="30"/>
@@ -9720,8 +9739,8 @@
       <c r="F67" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G67" s="37" t="s">
-        <v>212</v>
+      <c r="G67" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H67" s="30"/>
       <c r="I67" s="30"/>
@@ -9750,8 +9769,8 @@
       <c r="F68" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G68" s="37" t="s">
-        <v>212</v>
+      <c r="G68" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H68" s="30"/>
       <c r="I68" s="30"/>
@@ -9780,7 +9799,7 @@
       <c r="F69" s="30" t="n">
         <v>8.69</v>
       </c>
-      <c r="G69" s="37"/>
+      <c r="G69" s="36"/>
       <c r="H69" s="30"/>
       <c r="I69" s="30"/>
       <c r="J69" s="30"/>
@@ -9808,8 +9827,8 @@
       <c r="F70" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G70" s="37" t="s">
-        <v>212</v>
+      <c r="G70" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H70" s="30"/>
       <c r="I70" s="30"/>
@@ -9838,8 +9857,8 @@
       <c r="F71" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G71" s="37" t="s">
-        <v>212</v>
+      <c r="G71" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H71" s="30"/>
       <c r="I71" s="30"/>
@@ -9868,7 +9887,7 @@
       <c r="F72" s="30" t="n">
         <v>9.09</v>
       </c>
-      <c r="G72" s="37"/>
+      <c r="G72" s="36"/>
       <c r="H72" s="30"/>
       <c r="I72" s="30"/>
       <c r="J72" s="30"/>
@@ -9896,8 +9915,8 @@
       <c r="F73" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G73" s="37" t="s">
-        <v>212</v>
+      <c r="G73" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H73" s="30"/>
       <c r="I73" s="30"/>
@@ -9926,7 +9945,7 @@
       <c r="F74" s="30" t="n">
         <v>9.13</v>
       </c>
-      <c r="G74" s="37"/>
+      <c r="G74" s="36"/>
       <c r="H74" s="30"/>
       <c r="I74" s="30"/>
       <c r="J74" s="30"/>
@@ -9954,8 +9973,8 @@
       <c r="F75" s="30" t="n">
         <v>27.2</v>
       </c>
-      <c r="G75" s="37" t="s">
-        <v>206</v>
+      <c r="G75" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H75" s="30"/>
       <c r="I75" s="30" t="s">
@@ -9986,8 +10005,8 @@
       <c r="F76" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G76" s="37" t="s">
-        <v>212</v>
+      <c r="G76" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H76" s="30"/>
       <c r="I76" s="30"/>
@@ -10016,8 +10035,8 @@
       <c r="F77" s="30" t="n">
         <v>11.66</v>
       </c>
-      <c r="G77" s="37" t="s">
-        <v>206</v>
+      <c r="G77" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H77" s="30"/>
       <c r="I77" s="30" t="s">
@@ -10048,8 +10067,8 @@
       <c r="F78" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G78" s="37" t="s">
-        <v>212</v>
+      <c r="G78" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H78" s="30"/>
       <c r="I78" s="30" t="s">
@@ -10082,8 +10101,8 @@
       <c r="F79" s="30" t="n">
         <v>9.69</v>
       </c>
-      <c r="G79" s="37" t="s">
-        <v>206</v>
+      <c r="G79" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H79" s="30"/>
       <c r="I79" s="30" t="s">
@@ -10114,8 +10133,8 @@
       <c r="F80" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G80" s="37" t="s">
-        <v>212</v>
+      <c r="G80" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H80" s="30"/>
       <c r="I80" s="30" t="s">
@@ -10146,8 +10165,8 @@
       <c r="F81" s="30" t="n">
         <v>12.4</v>
       </c>
-      <c r="G81" s="37" t="s">
-        <v>206</v>
+      <c r="G81" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H81" s="30"/>
       <c r="I81" s="30" t="s">
@@ -10178,8 +10197,8 @@
       <c r="F82" s="30" t="n">
         <v>10.68</v>
       </c>
-      <c r="G82" s="37" t="s">
-        <v>206</v>
+      <c r="G82" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H82" s="30"/>
       <c r="I82" s="30" t="s">
@@ -10210,8 +10229,8 @@
       <c r="F83" s="30" t="n">
         <v>10.52</v>
       </c>
-      <c r="G83" s="37" t="s">
-        <v>206</v>
+      <c r="G83" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H83" s="30"/>
       <c r="I83" s="30" t="s">
@@ -10242,8 +10261,8 @@
       <c r="F84" s="30" t="n">
         <v>10.22</v>
       </c>
-      <c r="G84" s="37" t="s">
-        <v>206</v>
+      <c r="G84" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H84" s="30"/>
       <c r="I84" s="30" t="s">
@@ -10274,8 +10293,8 @@
       <c r="F85" s="30" t="n">
         <v>7.83</v>
       </c>
-      <c r="G85" s="37" t="s">
-        <v>206</v>
+      <c r="G85" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H85" s="30"/>
       <c r="I85" s="30" t="s">
@@ -10295,7 +10314,7 @@
         <v>57</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D86" s="30" t="n">
         <v>9</v>
@@ -10306,8 +10325,8 @@
       <c r="F86" s="30" t="n">
         <v>12.04</v>
       </c>
-      <c r="G86" s="37" t="s">
-        <v>206</v>
+      <c r="G86" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H86" s="30"/>
       <c r="I86" s="30" t="s">
@@ -10334,7 +10353,7 @@
       </c>
       <c r="E87" s="30"/>
       <c r="F87" s="30"/>
-      <c r="G87" s="37"/>
+      <c r="G87" s="36"/>
       <c r="H87" s="30"/>
       <c r="I87" s="30" t="s">
         <v>154</v>
@@ -10345,7 +10364,7 @@
       <c r="M87" s="30"/>
       <c r="N87" s="30"/>
     </row>
-    <row r="88" s="39" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" s="38" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="29" t="n">
         <v>45250</v>
       </c>
@@ -10364,138 +10383,138 @@
       <c r="F88" s="30" t="n">
         <v>12.6</v>
       </c>
-      <c r="G88" s="37" t="s">
-        <v>206</v>
+      <c r="G88" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H88" s="30"/>
       <c r="I88" s="30" t="s">
         <v>155</v>
       </c>
       <c r="J88" s="30"/>
-      <c r="K88" s="38"/>
-      <c r="L88" s="38"/>
-      <c r="M88" s="38"/>
-      <c r="N88" s="38"/>
-    </row>
-    <row r="89" s="39" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K88" s="37"/>
+      <c r="L88" s="37"/>
+      <c r="M88" s="37"/>
+      <c r="N88" s="37"/>
+    </row>
+    <row r="89" s="38" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="29" t="n">
         <v>45250</v>
       </c>
-      <c r="B89" s="38" t="s">
+      <c r="B89" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="C89" s="38" t="s">
+      <c r="C89" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="D89" s="38" t="n">
+      <c r="D89" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="E89" s="38" t="s">
+      <c r="E89" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="F89" s="38" t="n">
+      <c r="F89" s="37" t="n">
         <v>9.68</v>
       </c>
-      <c r="G89" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="H89" s="38"/>
-      <c r="I89" s="38" t="s">
+      <c r="G89" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="H89" s="37"/>
+      <c r="I89" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="J89" s="38"/>
-      <c r="K89" s="38"/>
-      <c r="L89" s="38"/>
-      <c r="M89" s="38"/>
-      <c r="N89" s="38"/>
-    </row>
-    <row r="90" s="39" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J89" s="37"/>
+      <c r="K89" s="37"/>
+      <c r="L89" s="37"/>
+      <c r="M89" s="37"/>
+      <c r="N89" s="37"/>
+    </row>
+    <row r="90" s="38" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="29" t="n">
         <v>45250</v>
       </c>
-      <c r="B90" s="38" t="s">
+      <c r="B90" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="C90" s="38" t="s">
+      <c r="C90" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="D90" s="38" t="n">
+      <c r="D90" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="E90" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="38" t="n">
+      <c r="E90" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" s="37" t="n">
         <v>30</v>
       </c>
-      <c r="G90" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="H90" s="38"/>
-      <c r="I90" s="38" t="s">
+      <c r="G90" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="H90" s="37"/>
+      <c r="I90" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J90" s="38"/>
-      <c r="K90" s="38"/>
-      <c r="L90" s="38"/>
-      <c r="M90" s="38"/>
-      <c r="N90" s="38"/>
-    </row>
-    <row r="91" s="39" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J90" s="37"/>
+      <c r="K90" s="37"/>
+      <c r="L90" s="37"/>
+      <c r="M90" s="37"/>
+      <c r="N90" s="37"/>
+    </row>
+    <row r="91" s="38" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="29" t="n">
         <v>45250</v>
       </c>
-      <c r="B91" s="38" t="s">
+      <c r="B91" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="C91" s="38" t="s">
+      <c r="C91" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="D91" s="38" t="n">
+      <c r="D91" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="E91" s="38" t="s">
+      <c r="E91" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="F91" s="38" t="n">
+      <c r="F91" s="37" t="n">
         <v>30</v>
       </c>
-      <c r="G91" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="H91" s="38"/>
-      <c r="I91" s="38" t="s">
+      <c r="G91" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="H91" s="37"/>
+      <c r="I91" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J91" s="38"/>
-      <c r="K91" s="38"/>
-      <c r="L91" s="38"/>
-      <c r="M91" s="38"/>
-      <c r="N91" s="38"/>
+      <c r="J91" s="37"/>
+      <c r="K91" s="37"/>
+      <c r="L91" s="37"/>
+      <c r="M91" s="37"/>
+      <c r="N91" s="37"/>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="29" t="n">
         <v>45250</v>
       </c>
-      <c r="B92" s="38" t="s">
+      <c r="B92" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="C92" s="38" t="s">
+      <c r="C92" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="D92" s="38" t="n">
+      <c r="D92" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="E92" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" s="38"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="38"/>
-      <c r="I92" s="38" t="s">
+      <c r="E92" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" s="37"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="37"/>
+      <c r="I92" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="J92" s="38"/>
+      <c r="J92" s="37"/>
       <c r="K92" s="30"/>
       <c r="L92" s="30"/>
       <c r="M92" s="30"/>
@@ -10520,8 +10539,8 @@
       <c r="F93" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G93" s="37" t="s">
-        <v>212</v>
+      <c r="G93" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H93" s="30"/>
       <c r="I93" s="30" t="s">
@@ -10552,8 +10571,8 @@
       <c r="F94" s="30" t="n">
         <v>15.45</v>
       </c>
-      <c r="G94" s="37" t="s">
-        <v>206</v>
+      <c r="G94" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H94" s="30"/>
       <c r="I94" s="30" t="s">
@@ -10584,12 +10603,12 @@
       <c r="F95" s="30" t="n">
         <v>10.27</v>
       </c>
-      <c r="G95" s="37" t="s">
-        <v>206</v>
+      <c r="G95" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H95" s="30"/>
       <c r="I95" s="30" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
@@ -10611,13 +10630,13 @@
         <v>2</v>
       </c>
       <c r="E96" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F96" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G96" s="37" t="s">
-        <v>212</v>
+      <c r="G96" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H96" s="30"/>
       <c r="I96" s="30"/>
@@ -10646,8 +10665,8 @@
       <c r="F97" s="30" t="n">
         <v>9.15</v>
       </c>
-      <c r="G97" s="37" t="s">
-        <v>206</v>
+      <c r="G97" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H97" s="30"/>
       <c r="I97" s="30"/>
@@ -10671,17 +10690,17 @@
         <v>4</v>
       </c>
       <c r="E98" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F98" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G98" s="37" t="s">
-        <v>212</v>
+      <c r="G98" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H98" s="30"/>
       <c r="I98" s="30" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
@@ -10708,12 +10727,12 @@
       <c r="F99" s="30" t="n">
         <v>9.81</v>
       </c>
-      <c r="G99" s="37" t="s">
-        <v>206</v>
+      <c r="G99" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H99" s="30"/>
       <c r="I99" s="30" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
@@ -10735,13 +10754,13 @@
         <v>6</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F100" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G100" s="37" t="s">
-        <v>212</v>
+      <c r="G100" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H100" s="30"/>
       <c r="I100" s="30"/>
@@ -10770,12 +10789,12 @@
       <c r="F101" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G101" s="37" t="s">
-        <v>212</v>
+      <c r="G101" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H101" s="30"/>
       <c r="I101" s="30" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
@@ -10802,12 +10821,12 @@
       <c r="F102" s="30" t="n">
         <v>9.74</v>
       </c>
-      <c r="G102" s="37" t="s">
-        <v>206</v>
+      <c r="G102" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H102" s="30"/>
       <c r="I102" s="30" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
@@ -10834,12 +10853,12 @@
       <c r="F103" s="30" t="n">
         <v>15.25</v>
       </c>
-      <c r="G103" s="37" t="s">
-        <v>206</v>
+      <c r="G103" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H103" s="30"/>
       <c r="I103" s="30" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
@@ -10866,12 +10885,12 @@
       <c r="F104" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G104" s="37" t="s">
-        <v>212</v>
+      <c r="G104" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H104" s="30"/>
       <c r="I104" s="30" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
@@ -10898,8 +10917,8 @@
       <c r="F105" s="30" t="n">
         <v>11.53</v>
       </c>
-      <c r="G105" s="37" t="s">
-        <v>206</v>
+      <c r="G105" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H105" s="30"/>
       <c r="I105" s="30"/>
@@ -10928,8 +10947,8 @@
       <c r="F106" s="30" t="n">
         <v>24.2</v>
       </c>
-      <c r="G106" s="37" t="s">
-        <v>206</v>
+      <c r="G106" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H106" s="30"/>
       <c r="I106" s="30"/>
@@ -10958,8 +10977,8 @@
       <c r="F107" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G107" s="37" t="s">
-        <v>212</v>
+      <c r="G107" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H107" s="30"/>
       <c r="I107" s="30"/>
@@ -10988,8 +11007,8 @@
       <c r="F108" s="30" t="n">
         <v>11.09</v>
       </c>
-      <c r="G108" s="37" t="s">
-        <v>206</v>
+      <c r="G108" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H108" s="30"/>
       <c r="I108" s="30"/>
@@ -11018,8 +11037,8 @@
       <c r="F109" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G109" s="37" t="s">
-        <v>212</v>
+      <c r="G109" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H109" s="30"/>
       <c r="I109" s="30"/>
@@ -11048,8 +11067,8 @@
       <c r="F110" s="30" t="n">
         <v>10.12</v>
       </c>
-      <c r="G110" s="37" t="s">
-        <v>206</v>
+      <c r="G110" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H110" s="30"/>
       <c r="I110" s="30" t="s">
@@ -11080,8 +11099,8 @@
       <c r="F111" s="30" t="n">
         <v>9.49</v>
       </c>
-      <c r="G111" s="37" t="s">
-        <v>206</v>
+      <c r="G111" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H111" s="30"/>
       <c r="I111" s="30" t="s">
@@ -11106,7 +11125,7 @@
       <c r="D112" s="30"/>
       <c r="E112" s="30"/>
       <c r="F112" s="30"/>
-      <c r="G112" s="37"/>
+      <c r="G112" s="36"/>
       <c r="H112" s="30"/>
       <c r="I112" s="30"/>
       <c r="J112" s="30"/>
@@ -11134,8 +11153,8 @@
       <c r="F113" s="30" t="n">
         <v>29.46</v>
       </c>
-      <c r="G113" s="37" t="s">
-        <v>206</v>
+      <c r="G113" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H113" s="30"/>
       <c r="I113" s="30" t="s">
@@ -11166,7 +11185,7 @@
       <c r="F114" s="30" t="n">
         <v>10.93</v>
       </c>
-      <c r="G114" s="37"/>
+      <c r="G114" s="36"/>
       <c r="H114" s="30"/>
       <c r="I114" s="30" t="s">
         <v>54</v>
@@ -11196,12 +11215,12 @@
       <c r="F115" s="30" t="n">
         <v>11.85</v>
       </c>
-      <c r="G115" s="37" t="s">
-        <v>206</v>
+      <c r="G115" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H115" s="30"/>
       <c r="I115" s="30" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
@@ -11228,8 +11247,8 @@
       <c r="F116" s="30" t="n">
         <v>18.88</v>
       </c>
-      <c r="G116" s="37" t="s">
-        <v>206</v>
+      <c r="G116" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H116" s="30"/>
       <c r="I116" s="30"/>
@@ -11258,8 +11277,8 @@
       <c r="F117" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G117" s="37" t="s">
-        <v>212</v>
+      <c r="G117" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H117" s="30"/>
       <c r="I117" s="30"/>
@@ -11288,8 +11307,8 @@
       <c r="F118" s="30" t="n">
         <v>10.94</v>
       </c>
-      <c r="G118" s="37" t="s">
-        <v>206</v>
+      <c r="G118" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H118" s="30"/>
       <c r="I118" s="30"/>
@@ -11318,8 +11337,8 @@
       <c r="F119" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G119" s="37" t="s">
-        <v>212</v>
+      <c r="G119" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H119" s="30"/>
       <c r="I119" s="30"/>
@@ -11348,8 +11367,8 @@
       <c r="F120" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G120" s="37" t="s">
-        <v>212</v>
+      <c r="G120" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H120" s="30"/>
       <c r="I120" s="30"/>
@@ -11378,8 +11397,8 @@
       <c r="F121" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G121" s="37" t="s">
-        <v>212</v>
+      <c r="G121" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H121" s="30"/>
       <c r="I121" s="30"/>
@@ -11408,8 +11427,8 @@
       <c r="F122" s="30" t="n">
         <v>11.93</v>
       </c>
-      <c r="G122" s="37" t="s">
-        <v>206</v>
+      <c r="G122" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H122" s="30"/>
       <c r="I122" s="30"/>
@@ -11438,8 +11457,8 @@
       <c r="F123" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G123" s="37" t="s">
-        <v>212</v>
+      <c r="G123" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H123" s="30"/>
       <c r="I123" s="30"/>
@@ -11468,8 +11487,8 @@
       <c r="F124" s="30" t="n">
         <v>10.48</v>
       </c>
-      <c r="G124" s="37" t="s">
-        <v>206</v>
+      <c r="G124" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H124" s="30"/>
       <c r="I124" s="30"/>
@@ -11498,12 +11517,12 @@
       <c r="F125" s="30" t="n">
         <v>12.67</v>
       </c>
-      <c r="G125" s="37" t="s">
-        <v>206</v>
+      <c r="G125" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H125" s="30"/>
       <c r="I125" s="30" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
@@ -11530,8 +11549,8 @@
       <c r="F126" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G126" s="37" t="s">
-        <v>212</v>
+      <c r="G126" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H126" s="30"/>
       <c r="I126" s="30"/>
@@ -11560,8 +11579,8 @@
       <c r="F127" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G127" s="37" t="s">
-        <v>212</v>
+      <c r="G127" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H127" s="30"/>
       <c r="I127" s="30"/>
@@ -11590,8 +11609,8 @@
       <c r="F128" s="30" t="n">
         <v>12.8</v>
       </c>
-      <c r="G128" s="37" t="s">
-        <v>206</v>
+      <c r="G128" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H128" s="30"/>
       <c r="I128" s="30"/>
@@ -11620,8 +11639,8 @@
       <c r="F129" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G129" s="37" t="s">
-        <v>212</v>
+      <c r="G129" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H129" s="30"/>
       <c r="I129" s="30"/>
@@ -11650,8 +11669,8 @@
       <c r="F130" s="30" t="n">
         <v>10.01</v>
       </c>
-      <c r="G130" s="37" t="s">
-        <v>206</v>
+      <c r="G130" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H130" s="30"/>
       <c r="I130" s="30" t="s">
@@ -11682,8 +11701,8 @@
       <c r="F131" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G131" s="37" t="s">
-        <v>212</v>
+      <c r="G131" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H131" s="30"/>
       <c r="I131" s="30"/>
@@ -11712,8 +11731,8 @@
       <c r="F132" s="30" t="n">
         <v>9.8</v>
       </c>
-      <c r="G132" s="37" t="s">
-        <v>206</v>
+      <c r="G132" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H132" s="30"/>
       <c r="I132" s="30"/>
@@ -11742,8 +11761,8 @@
       <c r="F133" s="30" t="n">
         <v>20.87</v>
       </c>
-      <c r="G133" s="37" t="s">
-        <v>206</v>
+      <c r="G133" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H133" s="30"/>
       <c r="I133" s="30"/>
@@ -11772,8 +11791,8 @@
       <c r="F134" s="30" t="n">
         <v>9.35</v>
       </c>
-      <c r="G134" s="37" t="s">
-        <v>206</v>
+      <c r="G134" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H134" s="30"/>
       <c r="I134" s="30"/>
@@ -11802,8 +11821,8 @@
       <c r="F135" s="30" t="n">
         <v>8.95</v>
       </c>
-      <c r="G135" s="37" t="s">
-        <v>206</v>
+      <c r="G135" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H135" s="30"/>
       <c r="I135" s="30"/>
@@ -11832,8 +11851,8 @@
       <c r="F136" s="30" t="n">
         <v>10.57</v>
       </c>
-      <c r="G136" s="37" t="s">
-        <v>206</v>
+      <c r="G136" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H136" s="30"/>
       <c r="I136" s="30" t="s">
@@ -11864,12 +11883,12 @@
       <c r="F137" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G137" s="37" t="s">
-        <v>212</v>
+      <c r="G137" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H137" s="30"/>
       <c r="I137" s="30" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="J137" s="30"/>
       <c r="K137" s="30"/>
@@ -11896,8 +11915,8 @@
       <c r="F138" s="30" t="n">
         <v>9.48</v>
       </c>
-      <c r="G138" s="37" t="s">
-        <v>206</v>
+      <c r="G138" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H138" s="30"/>
       <c r="I138" s="30"/>
@@ -11926,8 +11945,8 @@
       <c r="F139" s="30" t="n">
         <v>11.14</v>
       </c>
-      <c r="G139" s="37" t="s">
-        <v>206</v>
+      <c r="G139" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H139" s="30"/>
       <c r="I139" s="30"/>
@@ -11956,8 +11975,8 @@
       <c r="F140" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G140" s="37" t="s">
-        <v>212</v>
+      <c r="G140" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H140" s="30"/>
       <c r="I140" s="30"/>
@@ -11986,8 +12005,8 @@
       <c r="F141" s="30" t="n">
         <v>13.46</v>
       </c>
-      <c r="G141" s="37" t="s">
-        <v>206</v>
+      <c r="G141" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H141" s="30"/>
       <c r="I141" s="30"/>
@@ -12016,8 +12035,8 @@
       <c r="F142" s="30" t="n">
         <v>8.49</v>
       </c>
-      <c r="G142" s="37" t="s">
-        <v>206</v>
+      <c r="G142" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H142" s="30"/>
       <c r="I142" s="30"/>
@@ -12046,8 +12065,8 @@
       <c r="F143" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G143" s="37" t="s">
-        <v>212</v>
+      <c r="G143" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H143" s="30"/>
       <c r="I143" s="30" t="s">
@@ -12078,8 +12097,8 @@
       <c r="F144" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G144" s="37" t="s">
-        <v>212</v>
+      <c r="G144" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H144" s="30"/>
       <c r="I144" s="30" t="s">
@@ -12110,8 +12129,8 @@
       <c r="F145" s="30" t="n">
         <v>11.01</v>
       </c>
-      <c r="G145" s="37" t="s">
-        <v>206</v>
+      <c r="G145" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H145" s="30"/>
       <c r="I145" s="30"/>
@@ -12140,8 +12159,8 @@
       <c r="F146" s="30" t="n">
         <v>12.99</v>
       </c>
-      <c r="G146" s="37" t="s">
-        <v>206</v>
+      <c r="G146" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H146" s="30"/>
       <c r="I146" s="30" t="s">
@@ -12172,8 +12191,8 @@
       <c r="F147" s="30" t="n">
         <v>10.07</v>
       </c>
-      <c r="G147" s="37" t="s">
-        <v>206</v>
+      <c r="G147" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H147" s="30"/>
       <c r="I147" s="30"/>
@@ -12202,8 +12221,8 @@
       <c r="F148" s="30" t="n">
         <v>12.67</v>
       </c>
-      <c r="G148" s="37" t="s">
-        <v>206</v>
+      <c r="G148" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H148" s="30"/>
       <c r="I148" s="30" t="s">
@@ -12234,8 +12253,8 @@
       <c r="F149" s="30" t="n">
         <v>9.87</v>
       </c>
-      <c r="G149" s="37" t="s">
-        <v>206</v>
+      <c r="G149" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H149" s="30"/>
       <c r="I149" s="30"/>
@@ -12264,8 +12283,8 @@
       <c r="F150" s="30" t="n">
         <v>12.41</v>
       </c>
-      <c r="G150" s="37" t="s">
-        <v>206</v>
+      <c r="G150" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H150" s="30"/>
       <c r="I150" s="30"/>
@@ -12294,8 +12313,8 @@
       <c r="F151" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G151" s="37" t="s">
-        <v>212</v>
+      <c r="G151" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H151" s="30"/>
       <c r="I151" s="30"/>
@@ -12324,8 +12343,8 @@
       <c r="F152" s="30" t="n">
         <v>11.2</v>
       </c>
-      <c r="G152" s="37" t="s">
-        <v>206</v>
+      <c r="G152" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H152" s="30"/>
       <c r="I152" s="30"/>
@@ -12354,8 +12373,8 @@
       <c r="F153" s="30" t="n">
         <v>10.4</v>
       </c>
-      <c r="G153" s="37" t="s">
-        <v>206</v>
+      <c r="G153" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H153" s="30"/>
       <c r="I153" s="30"/>
@@ -12384,8 +12403,8 @@
       <c r="F154" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G154" s="37" t="s">
-        <v>212</v>
+      <c r="G154" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H154" s="30"/>
       <c r="I154" s="30"/>
@@ -12414,8 +12433,8 @@
       <c r="F155" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G155" s="37" t="s">
-        <v>212</v>
+      <c r="G155" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H155" s="30"/>
       <c r="I155" s="30"/>
@@ -12444,8 +12463,8 @@
       <c r="F156" s="30" t="n">
         <v>10.2</v>
       </c>
-      <c r="G156" s="37" t="s">
-        <v>206</v>
+      <c r="G156" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H156" s="30"/>
       <c r="I156" s="30"/>
@@ -12474,8 +12493,8 @@
       <c r="F157" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G157" s="37" t="s">
-        <v>212</v>
+      <c r="G157" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H157" s="30"/>
       <c r="I157" s="30"/>
@@ -12504,8 +12523,8 @@
       <c r="F158" s="30" t="n">
         <v>11.39</v>
       </c>
-      <c r="G158" s="37" t="s">
-        <v>206</v>
+      <c r="G158" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H158" s="30"/>
       <c r="I158" s="30"/>
@@ -12534,8 +12553,8 @@
       <c r="F159" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G159" s="37" t="s">
-        <v>212</v>
+      <c r="G159" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H159" s="30"/>
       <c r="I159" s="30"/>
@@ -12564,8 +12583,8 @@
       <c r="F160" s="30" t="n">
         <v>9.29</v>
       </c>
-      <c r="G160" s="37" t="s">
-        <v>206</v>
+      <c r="G160" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H160" s="30"/>
       <c r="I160" s="30" t="s">
@@ -12596,8 +12615,8 @@
       <c r="F161" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G161" s="37" t="s">
-        <v>212</v>
+      <c r="G161" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H161" s="30"/>
       <c r="I161" s="30"/>
@@ -12626,8 +12645,8 @@
       <c r="F162" s="30" t="n">
         <v>10.36</v>
       </c>
-      <c r="G162" s="37" t="s">
-        <v>206</v>
+      <c r="G162" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H162" s="30"/>
       <c r="I162" s="30"/>
@@ -12656,8 +12675,8 @@
       <c r="F163" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G163" s="37" t="s">
-        <v>212</v>
+      <c r="G163" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H163" s="30"/>
       <c r="I163" s="30"/>
@@ -12686,8 +12705,8 @@
       <c r="F164" s="30" t="n">
         <v>9.87</v>
       </c>
-      <c r="G164" s="37" t="s">
-        <v>206</v>
+      <c r="G164" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H164" s="30"/>
       <c r="I164" s="30"/>
@@ -12716,8 +12735,8 @@
       <c r="F165" s="30" t="n">
         <v>9.33</v>
       </c>
-      <c r="G165" s="37" t="s">
-        <v>206</v>
+      <c r="G165" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H165" s="30"/>
       <c r="I165" s="30"/>
@@ -12746,8 +12765,8 @@
       <c r="F166" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G166" s="37" t="s">
-        <v>212</v>
+      <c r="G166" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H166" s="30"/>
       <c r="I166" s="30"/>
@@ -12776,8 +12795,8 @@
       <c r="F167" s="30" t="n">
         <v>8.76</v>
       </c>
-      <c r="G167" s="37" t="s">
-        <v>206</v>
+      <c r="G167" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H167" s="30"/>
       <c r="I167" s="30"/>
@@ -12806,8 +12825,8 @@
       <c r="F168" s="30" t="n">
         <v>9.22</v>
       </c>
-      <c r="G168" s="37" t="s">
-        <v>206</v>
+      <c r="G168" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H168" s="30"/>
       <c r="I168" s="30"/>
@@ -12836,8 +12855,8 @@
       <c r="F169" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G169" s="37" t="s">
-        <v>212</v>
+      <c r="G169" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H169" s="30"/>
       <c r="I169" s="30"/>
@@ -12866,8 +12885,8 @@
       <c r="F170" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G170" s="37" t="s">
-        <v>212</v>
+      <c r="G170" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H170" s="30"/>
       <c r="I170" s="30"/>
@@ -12896,8 +12915,8 @@
       <c r="F171" s="30" t="n">
         <v>9.43</v>
       </c>
-      <c r="G171" s="37" t="s">
-        <v>206</v>
+      <c r="G171" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H171" s="30"/>
       <c r="I171" s="30"/>
@@ -12926,8 +12945,8 @@
       <c r="F172" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G172" s="37" t="s">
-        <v>212</v>
+      <c r="G172" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H172" s="30"/>
       <c r="I172" s="30"/>
@@ -12956,8 +12975,8 @@
       <c r="F173" s="30" t="n">
         <v>9.66</v>
       </c>
-      <c r="G173" s="37" t="s">
-        <v>206</v>
+      <c r="G173" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H173" s="30"/>
       <c r="I173" s="30"/>
@@ -12986,8 +13005,8 @@
       <c r="F174" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G174" s="37" t="s">
-        <v>212</v>
+      <c r="G174" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H174" s="30"/>
       <c r="I174" s="30"/>
@@ -13016,8 +13035,8 @@
       <c r="F175" s="30" t="n">
         <v>27.17</v>
       </c>
-      <c r="G175" s="37" t="s">
-        <v>206</v>
+      <c r="G175" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H175" s="30"/>
       <c r="I175" s="30" t="s">
@@ -13048,8 +13067,8 @@
       <c r="F176" s="30" t="n">
         <v>11.2</v>
       </c>
-      <c r="G176" s="37" t="s">
-        <v>206</v>
+      <c r="G176" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H176" s="30"/>
       <c r="I176" s="30" t="s">
@@ -13080,8 +13099,8 @@
       <c r="F177" s="30" t="n">
         <v>10.14</v>
       </c>
-      <c r="G177" s="37" t="s">
-        <v>206</v>
+      <c r="G177" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H177" s="30"/>
       <c r="I177" s="30"/>
@@ -13110,8 +13129,8 @@
       <c r="F178" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G178" s="37" t="s">
-        <v>212</v>
+      <c r="G178" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H178" s="30"/>
       <c r="I178" s="30"/>
@@ -13140,8 +13159,8 @@
       <c r="F179" s="30" t="n">
         <v>10.79</v>
       </c>
-      <c r="G179" s="37" t="s">
-        <v>206</v>
+      <c r="G179" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H179" s="30"/>
       <c r="I179" s="30" t="s">
@@ -13172,8 +13191,8 @@
       <c r="F180" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G180" s="37" t="s">
-        <v>212</v>
+      <c r="G180" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H180" s="30"/>
       <c r="I180" s="30"/>
@@ -13202,8 +13221,8 @@
       <c r="F181" s="30" t="n">
         <v>9.87</v>
       </c>
-      <c r="G181" s="37" t="s">
-        <v>206</v>
+      <c r="G181" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H181" s="30"/>
       <c r="I181" s="30"/>
@@ -13232,8 +13251,8 @@
       <c r="F182" s="30" t="n">
         <v>10.87</v>
       </c>
-      <c r="G182" s="37" t="s">
-        <v>206</v>
+      <c r="G182" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H182" s="30"/>
       <c r="I182" s="30"/>
@@ -13262,8 +13281,8 @@
       <c r="F183" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G183" s="37" t="s">
-        <v>212</v>
+      <c r="G183" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H183" s="30"/>
       <c r="I183" s="30" t="s">
@@ -13294,8 +13313,8 @@
       <c r="F184" s="30" t="n">
         <v>10.13</v>
       </c>
-      <c r="G184" s="37" t="s">
-        <v>206</v>
+      <c r="G184" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H184" s="30"/>
       <c r="I184" s="30"/>
@@ -13324,8 +13343,8 @@
       <c r="F185" s="30" t="n">
         <v>10.22</v>
       </c>
-      <c r="G185" s="37" t="s">
-        <v>206</v>
+      <c r="G185" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H185" s="30"/>
       <c r="I185" s="30"/>
@@ -13354,8 +13373,8 @@
       <c r="F186" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G186" s="37" t="s">
-        <v>212</v>
+      <c r="G186" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H186" s="30"/>
       <c r="I186" s="30"/>
@@ -13384,8 +13403,8 @@
       <c r="F187" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G187" s="37" t="s">
-        <v>212</v>
+      <c r="G187" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H187" s="30"/>
       <c r="I187" s="30"/>
@@ -13414,8 +13433,8 @@
       <c r="F188" s="30" t="n">
         <v>10.87</v>
       </c>
-      <c r="G188" s="37" t="s">
-        <v>206</v>
+      <c r="G188" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H188" s="30"/>
       <c r="I188" s="30" t="s">
@@ -13446,8 +13465,8 @@
       <c r="F189" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G189" s="37" t="s">
-        <v>212</v>
+      <c r="G189" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H189" s="30"/>
       <c r="I189" s="30"/>
@@ -13476,8 +13495,8 @@
       <c r="F190" s="30" t="n">
         <v>10.87</v>
       </c>
-      <c r="G190" s="37" t="s">
-        <v>206</v>
+      <c r="G190" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H190" s="30"/>
       <c r="I190" s="30"/>
@@ -13506,8 +13525,8 @@
       <c r="F191" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G191" s="37" t="s">
-        <v>212</v>
+      <c r="G191" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H191" s="30"/>
       <c r="I191" s="30"/>
@@ -13536,8 +13555,8 @@
       <c r="F192" s="30" t="n">
         <v>7.99</v>
       </c>
-      <c r="G192" s="37" t="s">
-        <v>206</v>
+      <c r="G192" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H192" s="30"/>
       <c r="I192" s="30"/>
@@ -13566,8 +13585,8 @@
       <c r="F193" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G193" s="37" t="s">
-        <v>212</v>
+      <c r="G193" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H193" s="30"/>
       <c r="I193" s="30" t="s">
@@ -13598,8 +13617,8 @@
       <c r="F194" s="30" t="n">
         <v>9.14</v>
       </c>
-      <c r="G194" s="37" t="s">
-        <v>206</v>
+      <c r="G194" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H194" s="30"/>
       <c r="I194" s="30" t="s">
@@ -13630,8 +13649,8 @@
       <c r="F195" s="30" t="n">
         <v>18.01</v>
       </c>
-      <c r="G195" s="37" t="s">
-        <v>206</v>
+      <c r="G195" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H195" s="30"/>
       <c r="I195" s="30" t="s">
@@ -13662,8 +13681,8 @@
       <c r="F196" s="30" t="n">
         <v>10.56</v>
       </c>
-      <c r="G196" s="37" t="s">
-        <v>206</v>
+      <c r="G196" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H196" s="30"/>
       <c r="I196" s="30"/>
@@ -13692,8 +13711,8 @@
       <c r="F197" s="30" t="n">
         <v>9.22</v>
       </c>
-      <c r="G197" s="37" t="s">
-        <v>206</v>
+      <c r="G197" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H197" s="30"/>
       <c r="I197" s="30" t="s">
@@ -13724,8 +13743,8 @@
       <c r="F198" s="30" t="n">
         <v>9.55</v>
       </c>
-      <c r="G198" s="37" t="s">
-        <v>206</v>
+      <c r="G198" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H198" s="30"/>
       <c r="I198" s="30"/>
@@ -13754,8 +13773,8 @@
       <c r="F199" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G199" s="37" t="s">
-        <v>212</v>
+      <c r="G199" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H199" s="30"/>
       <c r="I199" s="30"/>
@@ -13784,8 +13803,8 @@
       <c r="F200" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G200" s="37" t="s">
-        <v>212</v>
+      <c r="G200" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H200" s="30"/>
       <c r="I200" s="30"/>
@@ -13814,8 +13833,8 @@
       <c r="F201" s="30" t="n">
         <v>10.13</v>
       </c>
-      <c r="G201" s="37" t="s">
-        <v>206</v>
+      <c r="G201" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H201" s="30"/>
       <c r="I201" s="30"/>
@@ -13844,8 +13863,8 @@
       <c r="F202" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G202" s="37" t="s">
-        <v>212</v>
+      <c r="G202" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H202" s="30"/>
       <c r="I202" s="30"/>
@@ -13874,8 +13893,8 @@
       <c r="F203" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G203" s="37" t="s">
-        <v>212</v>
+      <c r="G203" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H203" s="30"/>
       <c r="I203" s="30"/>
@@ -13904,8 +13923,8 @@
       <c r="F204" s="30" t="n">
         <v>9.63</v>
       </c>
-      <c r="G204" s="37" t="s">
-        <v>206</v>
+      <c r="G204" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H204" s="30"/>
       <c r="I204" s="30" t="s">
@@ -13936,8 +13955,8 @@
       <c r="F205" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G205" s="37" t="s">
-        <v>212</v>
+      <c r="G205" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H205" s="30"/>
       <c r="I205" s="30"/>
@@ -13966,8 +13985,8 @@
       <c r="F206" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G206" s="37" t="s">
-        <v>212</v>
+      <c r="G206" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H206" s="30"/>
       <c r="I206" s="30"/>
@@ -13996,8 +14015,8 @@
       <c r="F207" s="30" t="n">
         <v>8.23</v>
       </c>
-      <c r="G207" s="37" t="s">
-        <v>206</v>
+      <c r="G207" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H207" s="30"/>
       <c r="I207" s="30" t="s">
@@ -14028,8 +14047,8 @@
       <c r="F208" s="30" t="n">
         <v>25.39</v>
       </c>
-      <c r="G208" s="37" t="s">
-        <v>206</v>
+      <c r="G208" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H208" s="30"/>
       <c r="I208" s="30"/>
@@ -14058,8 +14077,8 @@
       <c r="F209" s="30" t="n">
         <v>8.16</v>
       </c>
-      <c r="G209" s="37" t="s">
-        <v>206</v>
+      <c r="G209" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H209" s="30"/>
       <c r="I209" s="30"/>
@@ -14088,8 +14107,8 @@
       <c r="F210" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G210" s="37" t="s">
-        <v>212</v>
+      <c r="G210" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H210" s="30"/>
       <c r="I210" s="30"/>
@@ -14118,8 +14137,8 @@
       <c r="F211" s="30" t="n">
         <v>9.48</v>
       </c>
-      <c r="G211" s="37" t="s">
-        <v>206</v>
+      <c r="G211" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H211" s="30"/>
       <c r="I211" s="30"/>
@@ -14148,8 +14167,8 @@
       <c r="F212" s="30" t="n">
         <v>8.82</v>
       </c>
-      <c r="G212" s="37" t="s">
-        <v>206</v>
+      <c r="G212" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H212" s="30"/>
       <c r="I212" s="30"/>
@@ -14178,8 +14197,8 @@
       <c r="F213" s="30" t="n">
         <v>9.14</v>
       </c>
-      <c r="G213" s="37" t="s">
-        <v>206</v>
+      <c r="G213" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H213" s="30"/>
       <c r="I213" s="30"/>
@@ -14208,8 +14227,8 @@
       <c r="F214" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G214" s="37" t="s">
-        <v>212</v>
+      <c r="G214" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H214" s="30"/>
       <c r="I214" s="30"/>
@@ -14238,8 +14257,8 @@
       <c r="F215" s="30" t="n">
         <v>8.6</v>
       </c>
-      <c r="G215" s="37" t="s">
-        <v>206</v>
+      <c r="G215" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H215" s="30"/>
       <c r="I215" s="30"/>
@@ -14268,8 +14287,8 @@
       <c r="F216" s="30" t="n">
         <v>8.95</v>
       </c>
-      <c r="G216" s="37" t="s">
-        <v>206</v>
+      <c r="G216" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H216" s="30"/>
       <c r="I216" s="30"/>
@@ -14298,8 +14317,8 @@
       <c r="F217" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G217" s="37" t="s">
-        <v>212</v>
+      <c r="G217" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H217" s="30"/>
       <c r="I217" s="30"/>
@@ -14328,8 +14347,8 @@
       <c r="F218" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G218" s="37" t="s">
-        <v>212</v>
+      <c r="G218" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H218" s="30"/>
       <c r="I218" s="30"/>
@@ -14358,8 +14377,8 @@
       <c r="F219" s="30" t="n">
         <v>9.08</v>
       </c>
-      <c r="G219" s="37" t="s">
-        <v>206</v>
+      <c r="G219" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H219" s="30"/>
       <c r="I219" s="30"/>
@@ -14388,8 +14407,8 @@
       <c r="F220" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G220" s="37" t="s">
-        <v>212</v>
+      <c r="G220" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H220" s="30"/>
       <c r="I220" s="30"/>
@@ -14418,8 +14437,8 @@
       <c r="F221" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G221" s="37" t="s">
-        <v>212</v>
+      <c r="G221" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H221" s="30"/>
       <c r="I221" s="30"/>
@@ -14448,8 +14467,8 @@
       <c r="F222" s="30" t="n">
         <v>7.62</v>
       </c>
-      <c r="G222" s="37" t="s">
-        <v>206</v>
+      <c r="G222" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H222" s="30"/>
       <c r="I222" s="30"/>
@@ -14478,8 +14497,8 @@
       <c r="F223" s="30" t="n">
         <v>15.96</v>
       </c>
-      <c r="G223" s="37" t="s">
-        <v>206</v>
+      <c r="G223" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H223" s="30"/>
       <c r="I223" s="30"/>
@@ -14508,8 +14527,8 @@
       <c r="F224" s="30" t="n">
         <v>8.56</v>
       </c>
-      <c r="G224" s="37" t="s">
-        <v>206</v>
+      <c r="G224" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H224" s="30"/>
       <c r="I224" s="30"/>
@@ -14538,8 +14557,8 @@
       <c r="F225" s="30" t="n">
         <v>11.54</v>
       </c>
-      <c r="G225" s="37" t="s">
-        <v>206</v>
+      <c r="G225" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H225" s="30"/>
       <c r="I225" s="30"/>
@@ -14568,8 +14587,8 @@
       <c r="F226" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G226" s="37" t="s">
-        <v>212</v>
+      <c r="G226" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H226" s="30"/>
       <c r="I226" s="30"/>
@@ -14598,8 +14617,8 @@
       <c r="F227" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G227" s="37" t="s">
-        <v>212</v>
+      <c r="G227" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H227" s="30"/>
       <c r="I227" s="30"/>
@@ -14628,8 +14647,8 @@
       <c r="F228" s="30" t="n">
         <v>8.61</v>
       </c>
-      <c r="G228" s="37" t="s">
-        <v>206</v>
+      <c r="G228" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H228" s="30"/>
       <c r="I228" s="30"/>
@@ -14658,8 +14677,8 @@
       <c r="F229" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G229" s="37" t="s">
-        <v>212</v>
+      <c r="G229" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H229" s="30"/>
       <c r="I229" s="30"/>
@@ -14688,8 +14707,8 @@
       <c r="F230" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G230" s="37" t="s">
-        <v>212</v>
+      <c r="G230" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H230" s="30"/>
       <c r="I230" s="30"/>
@@ -14718,8 +14737,8 @@
       <c r="F231" s="30" t="n">
         <v>9.6</v>
       </c>
-      <c r="G231" s="37" t="s">
-        <v>206</v>
+      <c r="G231" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H231" s="30"/>
       <c r="I231" s="30"/>
@@ -14748,8 +14767,8 @@
       <c r="F232" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G232" s="37" t="s">
-        <v>212</v>
+      <c r="G232" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H232" s="30"/>
       <c r="I232" s="30"/>
@@ -14778,8 +14797,8 @@
       <c r="F233" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G233" s="37" t="s">
-        <v>212</v>
+      <c r="G233" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H233" s="30"/>
       <c r="I233" s="30"/>
@@ -14808,8 +14827,8 @@
       <c r="F234" s="30" t="n">
         <v>8.46</v>
       </c>
-      <c r="G234" s="37" t="s">
-        <v>206</v>
+      <c r="G234" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H234" s="30"/>
       <c r="I234" s="30"/>
@@ -14838,8 +14857,8 @@
       <c r="F235" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G235" s="37" t="s">
-        <v>212</v>
+      <c r="G235" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H235" s="30"/>
       <c r="I235" s="30"/>
@@ -14868,8 +14887,8 @@
       <c r="F236" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G236" s="37" t="s">
-        <v>212</v>
+      <c r="G236" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H236" s="30"/>
       <c r="I236" s="30"/>
@@ -14898,8 +14917,8 @@
       <c r="F237" s="30" t="n">
         <v>10.12</v>
       </c>
-      <c r="G237" s="37" t="s">
-        <v>206</v>
+      <c r="G237" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H237" s="30"/>
       <c r="I237" s="30"/>
@@ -14928,8 +14947,8 @@
       <c r="F238" s="30" t="n">
         <v>19.18</v>
       </c>
-      <c r="G238" s="37" t="s">
-        <v>206</v>
+      <c r="G238" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H238" s="30"/>
       <c r="I238" s="30"/>
@@ -14958,8 +14977,8 @@
       <c r="F239" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G239" s="37" t="s">
-        <v>212</v>
+      <c r="G239" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H239" s="30"/>
       <c r="I239" s="30"/>
@@ -14988,8 +15007,8 @@
       <c r="F240" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G240" s="37" t="s">
-        <v>212</v>
+      <c r="G240" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H240" s="30"/>
       <c r="I240" s="30"/>
@@ -15018,8 +15037,8 @@
       <c r="F241" s="30" t="n">
         <v>9.92</v>
       </c>
-      <c r="G241" s="37" t="s">
-        <v>206</v>
+      <c r="G241" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H241" s="30"/>
       <c r="I241" s="30"/>
@@ -15048,8 +15067,8 @@
       <c r="F242" s="30" t="n">
         <v>9.49</v>
       </c>
-      <c r="G242" s="37" t="s">
-        <v>206</v>
+      <c r="G242" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H242" s="30"/>
       <c r="I242" s="30"/>
@@ -15078,8 +15097,8 @@
       <c r="F243" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G243" s="37" t="s">
-        <v>212</v>
+      <c r="G243" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H243" s="30"/>
       <c r="I243" s="30"/>
@@ -15108,8 +15127,8 @@
       <c r="F244" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G244" s="37" t="s">
-        <v>212</v>
+      <c r="G244" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H244" s="30"/>
       <c r="I244" s="30"/>
@@ -15138,12 +15157,12 @@
       <c r="F245" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G245" s="37" t="s">
-        <v>212</v>
+      <c r="G245" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H245" s="30"/>
       <c r="I245" s="30" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="J245" s="30"/>
       <c r="K245" s="30"/>
@@ -15170,12 +15189,12 @@
       <c r="F246" s="30" t="n">
         <v>19.61</v>
       </c>
-      <c r="G246" s="37" t="s">
-        <v>206</v>
+      <c r="G246" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H246" s="30"/>
       <c r="I246" s="30" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J246" s="30"/>
       <c r="K246" s="30"/>
@@ -15202,8 +15221,8 @@
       <c r="F247" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G247" s="37" t="s">
-        <v>212</v>
+      <c r="G247" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H247" s="30"/>
       <c r="I247" s="30" t="s">
@@ -15234,8 +15253,8 @@
       <c r="F248" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G248" s="37" t="s">
-        <v>212</v>
+      <c r="G248" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H248" s="30"/>
       <c r="I248" s="30" t="s">
@@ -15266,8 +15285,8 @@
       <c r="F249" s="30" t="n">
         <v>8.87</v>
       </c>
-      <c r="G249" s="37" t="s">
-        <v>206</v>
+      <c r="G249" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H249" s="30"/>
       <c r="I249" s="30" t="s">
@@ -15298,8 +15317,8 @@
       <c r="F250" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G250" s="37" t="s">
-        <v>212</v>
+      <c r="G250" s="36" t="s">
+        <v>216</v>
       </c>
       <c r="H250" s="30"/>
       <c r="I250" s="30" t="s">
@@ -15330,8 +15349,8 @@
       <c r="F251" s="30" t="n">
         <v>8.09</v>
       </c>
-      <c r="G251" s="37" t="s">
-        <v>206</v>
+      <c r="G251" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="H251" s="30"/>
       <c r="I251" s="30" t="s">
@@ -15356,7 +15375,7 @@
       <c r="D252" s="30"/>
       <c r="E252" s="30"/>
       <c r="F252" s="30"/>
-      <c r="G252" s="37"/>
+      <c r="G252" s="36"/>
       <c r="H252" s="30"/>
       <c r="I252" s="30" t="s">
         <v>194</v>
@@ -15380,7 +15399,7 @@
       <c r="D253" s="30"/>
       <c r="E253" s="30"/>
       <c r="F253" s="30"/>
-      <c r="G253" s="37"/>
+      <c r="G253" s="36"/>
       <c r="H253" s="30"/>
       <c r="I253" s="30" t="s">
         <v>195</v>
